--- a/INPUTS/inputs.xlsx
+++ b/INPUTS/inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renoshpr/Documents/BLUE_CLOUD/SOCA_CHL_2020/NOTEBOOK/SOCA_LIGHT_MODELS/INPUTS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitytasmania-my.sharepoint.com/personal/jakob_weis_utas_edu_au/Documents/Work/Code/Library/SOCA-LIGHT-MODELS/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C853B44B-83DC-754C-A311-ADEB87EB7236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{C853B44B-83DC-754C-A311-ADEB87EB7236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FF6053-164A-4D4B-9884-52A209DF2DFA}"/>
   <bookViews>
-    <workbookView xWindow="38080" yWindow="6120" windowWidth="35200" windowHeight="17780" xr2:uid="{C2DFED53-C4FF-6D41-BB76-25657FE7805A}"/>
+    <workbookView xWindow="52740" yWindow="29720" windowWidth="29940" windowHeight="18560" xr2:uid="{C2DFED53-C4FF-6D41-BB76-25657FE7805A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>coriolis</t>
   </si>
   <si>
-    <t>/Users/renoshpr/Documents/ARGO_DAC/dac/coriolis/6901472/profiles/SD6901472_032.nc</t>
+    <t>/Users/jweis/Desktop/test_float/Profiles/6901472_Sprof.nc</t>
   </si>
 </sst>
 </file>
@@ -141,9 +141,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +181,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -287,7 +287,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,7 +429,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
